--- a/artfynd/A 48281-2025 artfynd.xlsx
+++ b/artfynd/A 48281-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>111369857</v>
       </c>
       <c r="B2" t="n">
-        <v>85003</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>88971</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -725,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>370279.2512165825</v>
+        <v>370280</v>
       </c>
       <c r="R2" t="n">
-        <v>6939856.562199191</v>
+        <v>6939857</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
